--- a/config/战争巨兽.xlsx
+++ b/config/战争巨兽.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数" sheetId="1" r:id="Ra0d02a24856744c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数" sheetId="1" r:id="R6ed819cfc24d41a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -68,8 +68,12 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -78,13 +82,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Parameters" displayName="Parameters" ref="A1:E55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="5">
-    <x:tableColumn id="1" name="参数ID（勿改）"/>
-    <x:tableColumn id="2" name="对象 / 参数"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Parameters" displayName="Parameters" ref="A1:F57" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="所属对象"/>
+    <x:tableColumn id="2" name="字段"/>
     <x:tableColumn id="3" name="配置值（修改此列）"/>
-    <x:tableColumn id="4" name="初始参考值"/>
-    <x:tableColumn id="5" name="来源"/>
+    <x:tableColumn id="4" name="类型"/>
+    <x:tableColumn id="5" name="填写说明"/>
+    <x:tableColumn id="6" name="唯一ID（勿改）"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -285,952 +290,1158 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="43" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="68" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>参数ID（勿改）</x:v>
+        <x:v>所属对象</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>对象 / 参数</x:v>
+        <x:v>字段</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
         <x:v>配置值（修改此列）</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>初始参考值</x:v>
+        <x:v>类型</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>来源</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
+        <x:v>填写说明</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>唯一ID（勿改）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.hp</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B2" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 生命值</x:v>
-      </x:c>
-      <x:c r="C2" s="5" t="n">
-        <x:v>120000</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="n">
-        <x:v>120000</x:v>
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="str">
+        <x:v>齐柏林飞艇</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E2" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.dmg</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B3" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 伤害</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="n">
-        <x:v>2400</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="n">
-        <x:v>2400</x:v>
+        <x:v>描述</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="str">
+        <x:v>120000生命 · 仅远程可命中 · 慢速巡航 · 只轰炸敌军</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E3" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.desc</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.range</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B4" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 攻击距离</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="n">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="n">
-        <x:v>650</x:v>
+        <x:v>生命值</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E4" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.hp</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.speed</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B5" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 移动速度</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="n">
-        <x:v>12</x:v>
+        <x:v>攻击伤害</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E5" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.dmg</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.atkCd</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B6" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 攻击间隔（秒）</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="n">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="n">
-        <x:v>1.4</x:v>
+        <x:v>攻击距离</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E6" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.range</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.bodyRadius</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B7" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / bodyRadius</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="n">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="n">
-        <x:v>145</x:v>
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E7" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.speed</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.cost</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B8" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 旧金币基数（四资源价格另设）</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>攻击间隔（秒）</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E8" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.atkCd</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.pop</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B9" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 人口占用</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>碰撞半径</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E9" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.bodyRadius</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="1" t="str">
-        <x:v>War.DEFS.zeppelin.tier</x:v>
+        <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B10" s="1" t="str">
-        <x:v>战争巨兽 / zeppelin / 时代</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>图标</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="str">
+        <x:v>assets/sprites/war_beasts.png#0,0,6,12</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E10" s="1" t="str">
-        <x:v>War.DEFS.zeppelin</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>assets 图片路径；图集追加 #行,帧,总行数,总帧数（从0开始）</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="str">
+        <x:v>War.DEFS.zeppelin.icon</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="1" t="str">
-        <x:v>War.DEFS.train.hp</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B11" s="1" t="str">
-        <x:v>战争巨兽 / train / 生命值</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="n">
-        <x:v>80000</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="n">
-        <x:v>80000</x:v>
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>装甲列车</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E11" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="str">
+        <x:v>War.DEFS.train.name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="1" t="str">
-        <x:v>War.DEFS.train.dmg</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B12" s="1" t="str">
-        <x:v>战争巨兽 / train / 伤害</x:v>
-      </x:c>
-      <x:c r="C12" s="5" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D12" s="6" t="n">
-        <x:v>72</x:v>
+        <x:v>描述</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="str">
+        <x:v>5节独立车厢×16000生命 · 加特林只扫射敌军 · 慢速往返</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E12" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="str">
+        <x:v>War.DEFS.train.desc</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1" t="str">
-        <x:v>War.DEFS.train.range</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B13" s="1" t="str">
-        <x:v>战争巨兽 / train / 攻击距离</x:v>
-      </x:c>
-      <x:c r="C13" s="5" t="n">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="D13" s="6" t="n">
-        <x:v>430</x:v>
+        <x:v>生命值</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="n">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E13" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="str">
+        <x:v>War.DEFS.train.hp</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="1" t="str">
-        <x:v>War.DEFS.train.speed</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B14" s="1" t="str">
-        <x:v>战争巨兽 / train / 移动速度</x:v>
-      </x:c>
-      <x:c r="C14" s="5" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D14" s="6" t="n">
-        <x:v>28</x:v>
+        <x:v>攻击伤害</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E14" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="str">
+        <x:v>War.DEFS.train.dmg</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="1" t="str">
-        <x:v>War.DEFS.train.atkCd</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B15" s="1" t="str">
-        <x:v>战争巨兽 / train / 攻击间隔（秒）</x:v>
-      </x:c>
-      <x:c r="C15" s="5" t="n">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="D15" s="6" t="n">
-        <x:v>0.18</x:v>
+        <x:v>攻击距离</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="n">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E15" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="str">
+        <x:v>War.DEFS.train.range</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="1" t="str">
-        <x:v>War.DEFS.train.bodyRadius</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B16" s="1" t="str">
-        <x:v>战争巨兽 / train / bodyRadius</x:v>
-      </x:c>
-      <x:c r="C16" s="5" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D16" s="6" t="n">
-        <x:v>180</x:v>
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E16" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="str">
+        <x:v>War.DEFS.train.speed</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="1" t="str">
-        <x:v>War.DEFS.train.cost</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B17" s="1" t="str">
-        <x:v>战争巨兽 / train / 旧金币基数（四资源价格另设）</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>攻击间隔（秒）</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E17" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="str">
+        <x:v>War.DEFS.train.atkCd</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="1" t="str">
-        <x:v>War.DEFS.train.pop</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B18" s="1" t="str">
-        <x:v>战争巨兽 / train / 人口占用</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>碰撞半径</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E18" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="str">
+        <x:v>War.DEFS.train.bodyRadius</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="1" t="str">
-        <x:v>War.DEFS.train.tier</x:v>
+        <x:v>装甲列车</x:v>
       </x:c>
       <x:c r="B19" s="1" t="str">
-        <x:v>战争巨兽 / train / 时代</x:v>
-      </x:c>
-      <x:c r="C19" s="5" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>图标</x:v>
+      </x:c>
+      <x:c r="C19" s="5" t="str">
+        <x:v>assets/sprites/war_beasts.png#1,0,6,12</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E19" s="1" t="str">
-        <x:v>War.DEFS.train</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>assets 图片路径；图集追加 #行,帧,总行数,总帧数（从0开始）</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="str">
+        <x:v>War.DEFS.train.icon</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="1" t="str">
-        <x:v>War.DEFS.mech.hp</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B20" s="1" t="str">
-        <x:v>战争巨兽 / mech / 生命值</x:v>
-      </x:c>
-      <x:c r="C20" s="5" t="n">
-        <x:v>90000</x:v>
-      </x:c>
-      <x:c r="D20" s="6" t="n">
-        <x:v>90000</x:v>
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="str">
+        <x:v>末日机甲</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E20" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="str">
+        <x:v>War.DEFS.mech.name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="1" t="str">
-        <x:v>War.DEFS.mech.dmg</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B21" s="1" t="str">
-        <x:v>战争巨兽 / mech / 伤害</x:v>
-      </x:c>
-      <x:c r="C21" s="5" t="n">
-        <x:v>680</x:v>
-      </x:c>
-      <x:c r="D21" s="6" t="n">
-        <x:v>680</x:v>
+        <x:v>描述</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="str">
+        <x:v>90000生命 · 重型巡航 · 每6秒随机技能 · 本体和技能不伤基地</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E21" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="str">
+        <x:v>War.DEFS.mech.desc</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="1" t="str">
-        <x:v>War.DEFS.mech.range</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B22" s="1" t="str">
-        <x:v>战争巨兽 / mech / 攻击距离</x:v>
-      </x:c>
-      <x:c r="C22" s="5" t="n">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="D22" s="6" t="n">
-        <x:v>330</x:v>
+        <x:v>生命值</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E22" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="str">
+        <x:v>War.DEFS.mech.hp</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="1" t="str">
-        <x:v>War.DEFS.mech.speed</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B23" s="1" t="str">
-        <x:v>战争巨兽 / mech / 移动速度</x:v>
-      </x:c>
-      <x:c r="C23" s="5" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D23" s="6" t="n">
-        <x:v>10</x:v>
+        <x:v>攻击伤害</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="n">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E23" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="str">
+        <x:v>War.DEFS.mech.dmg</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="1" t="str">
-        <x:v>War.DEFS.mech.atkCd</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B24" s="1" t="str">
-        <x:v>战争巨兽 / mech / 攻击间隔（秒）</x:v>
-      </x:c>
-      <x:c r="C24" s="5" t="n">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="D24" s="6" t="n">
-        <x:v>0.75</x:v>
+        <x:v>攻击距离</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E24" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="str">
+        <x:v>War.DEFS.mech.range</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="1" t="str">
-        <x:v>War.DEFS.mech.bodyRadius</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B25" s="1" t="str">
-        <x:v>战争巨兽 / mech / bodyRadius</x:v>
-      </x:c>
-      <x:c r="C25" s="5" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D25" s="6" t="n">
-        <x:v>80</x:v>
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E25" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="str">
+        <x:v>War.DEFS.mech.speed</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1" t="str">
-        <x:v>War.DEFS.mech.cost</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B26" s="1" t="str">
-        <x:v>战争巨兽 / mech / 旧金币基数（四资源价格另设）</x:v>
-      </x:c>
-      <x:c r="C26" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>攻击间隔（秒）</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E26" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="str">
+        <x:v>War.DEFS.mech.atkCd</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1" t="str">
-        <x:v>War.DEFS.mech.pop</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B27" s="1" t="str">
-        <x:v>战争巨兽 / mech / 人口占用</x:v>
-      </x:c>
-      <x:c r="C27" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>碰撞半径</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E27" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="str">
+        <x:v>War.DEFS.mech.bodyRadius</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="1" t="str">
-        <x:v>War.DEFS.mech.tier</x:v>
+        <x:v>末日机甲</x:v>
       </x:c>
       <x:c r="B28" s="1" t="str">
-        <x:v>战争巨兽 / mech / 时代</x:v>
-      </x:c>
-      <x:c r="C28" s="5" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D28" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>图标</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>assets/sprites/war_beasts.png#2,0,6,12</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E28" s="1" t="str">
-        <x:v>War.DEFS.mech</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
+        <x:v>assets 图片路径；图集追加 #行,帧,总行数,总帧数（从0开始）</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="str">
+        <x:v>War.DEFS.mech.icon</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="1" t="str">
-        <x:v>War.DEFS.portal.hp</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B29" s="1" t="str">
-        <x:v>战争巨兽 / portal / 生命值</x:v>
-      </x:c>
-      <x:c r="C29" s="5" t="n">
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="D29" s="6" t="n">
-        <x:v>100000</x:v>
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>噩梦传送门</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E29" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="str">
+        <x:v>War.DEFS.portal.name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
       <x:c r="A30" s="1" t="str">
-        <x:v>War.DEFS.portal.dmg</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B30" s="1" t="str">
-        <x:v>战争巨兽 / portal / 伤害</x:v>
-      </x:c>
-      <x:c r="C30" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>描述</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>100000生命的固定新基地 · 每秒随机产出3–5名全僵尸文明一至三阶援军，可攻城</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E30" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="str">
+        <x:v>War.DEFS.portal.desc</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="1" t="str">
-        <x:v>War.DEFS.portal.range</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B31" s="1" t="str">
-        <x:v>战争巨兽 / portal / 攻击距离</x:v>
-      </x:c>
-      <x:c r="C31" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>生命值</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E31" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="str">
+        <x:v>War.DEFS.portal.hp</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="1" t="str">
-        <x:v>War.DEFS.portal.speed</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B32" s="1" t="str">
-        <x:v>战争巨兽 / portal / 移动速度</x:v>
-      </x:c>
-      <x:c r="C32" s="5" t="n">
+        <x:v>攻击伤害</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D32" s="6" t="n">
-        <x:v>0</x:v>
+      <x:c r="D32" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E32" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="str">
+        <x:v>War.DEFS.portal.dmg</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="1" t="str">
-        <x:v>War.DEFS.portal.atkCd</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B33" s="1" t="str">
-        <x:v>战争巨兽 / portal / 攻击间隔（秒）</x:v>
-      </x:c>
-      <x:c r="C33" s="5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D33" s="6" t="n">
-        <x:v>1</x:v>
+        <x:v>攻击距离</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E33" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="str">
+        <x:v>War.DEFS.portal.range</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="1" t="str">
-        <x:v>War.DEFS.portal.bodyRadius</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B34" s="1" t="str">
-        <x:v>战争巨兽 / portal / bodyRadius</x:v>
-      </x:c>
-      <x:c r="C34" s="5" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D34" s="6" t="n">
-        <x:v>95</x:v>
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E34" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="str">
+        <x:v>War.DEFS.portal.speed</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="1" t="str">
-        <x:v>War.DEFS.portal.cost</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B35" s="1" t="str">
-        <x:v>战争巨兽 / portal / 旧金币基数（四资源价格另设）</x:v>
-      </x:c>
-      <x:c r="C35" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>攻击间隔（秒）</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E35" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="str">
+        <x:v>War.DEFS.portal.atkCd</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="1" t="str">
-        <x:v>War.DEFS.portal.pop</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B36" s="1" t="str">
-        <x:v>战争巨兽 / portal / 人口占用</x:v>
-      </x:c>
-      <x:c r="C36" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>碰撞半径</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E36" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="str">
+        <x:v>War.DEFS.portal.bodyRadius</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
       <x:c r="A37" s="1" t="str">
-        <x:v>War.DEFS.portal.tier</x:v>
+        <x:v>噩梦传送门</x:v>
       </x:c>
       <x:c r="B37" s="1" t="str">
-        <x:v>战争巨兽 / portal / 时代</x:v>
-      </x:c>
-      <x:c r="C37" s="5" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D37" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>图标</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="str">
+        <x:v>assets/sprites/war_beasts.png#3,0,6,12</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E37" s="1" t="str">
-        <x:v>War.DEFS.portal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>assets 图片路径；图集追加 #行,帧,总行数,总帧数（从0开始）</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="str">
+        <x:v>War.DEFS.portal.icon</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="1" t="str">
-        <x:v>War.DEFS.king.hp</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B38" s="1" t="str">
-        <x:v>战争巨兽 / king / 生命值</x:v>
-      </x:c>
-      <x:c r="C38" s="5" t="n">
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="D38" s="6" t="n">
-        <x:v>30000</x:v>
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C38" s="5" t="str">
+        <x:v>僵尸之王</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E38" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="str">
+        <x:v>War.DEFS.king.name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="36" customHeight="1">
       <x:c r="A39" s="1" t="str">
-        <x:v>War.DEFS.king.dmg</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B39" s="1" t="str">
-        <x:v>战争巨兽 / king / 伤害</x:v>
-      </x:c>
-      <x:c r="C39" s="5" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="D39" s="6" t="n">
-        <x:v>2800</x:v>
+        <x:v>描述</x:v>
+      </x:c>
+      <x:c r="C39" s="5" t="str">
+        <x:v>30000生命 · 正常承伤 · 极慢巡航 · 近战处决并重生普通敌军，不攻击基地</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E39" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="str">
+        <x:v>War.DEFS.king.desc</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="1" t="str">
-        <x:v>War.DEFS.king.range</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B40" s="1" t="str">
-        <x:v>战争巨兽 / king / 攻击距离</x:v>
-      </x:c>
-      <x:c r="C40" s="5" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D40" s="6" t="n">
-        <x:v>140</x:v>
+        <x:v>生命值</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="n">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E40" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="str">
+        <x:v>War.DEFS.king.hp</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="1" t="str">
-        <x:v>War.DEFS.king.speed</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B41" s="1" t="str">
-        <x:v>战争巨兽 / king / 移动速度</x:v>
-      </x:c>
-      <x:c r="C41" s="5" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D41" s="6" t="n">
-        <x:v>6</x:v>
+        <x:v>攻击伤害</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="n">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E41" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="str">
+        <x:v>War.DEFS.king.dmg</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="1" t="str">
-        <x:v>War.DEFS.king.atkCd</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B42" s="1" t="str">
-        <x:v>战争巨兽 / king / 攻击间隔（秒）</x:v>
-      </x:c>
-      <x:c r="C42" s="5" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="D42" s="6" t="n">
-        <x:v>4.5</x:v>
+        <x:v>攻击距离</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E42" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="str">
+        <x:v>War.DEFS.king.range</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="1" t="str">
-        <x:v>War.DEFS.king.bodyRadius</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B43" s="1" t="str">
-        <x:v>战争巨兽 / king / bodyRadius</x:v>
-      </x:c>
-      <x:c r="C43" s="5" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D43" s="6" t="n">
-        <x:v>90</x:v>
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E43" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="str">
+        <x:v>War.DEFS.king.speed</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="1" t="str">
-        <x:v>War.DEFS.king.cost</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B44" s="1" t="str">
-        <x:v>战争巨兽 / king / 旧金币基数（四资源价格另设）</x:v>
-      </x:c>
-      <x:c r="C44" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D44" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>攻击间隔（秒）</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E44" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="str">
+        <x:v>War.DEFS.king.atkCd</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="1" t="str">
-        <x:v>War.DEFS.king.pop</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B45" s="1" t="str">
-        <x:v>战争巨兽 / king / 人口占用</x:v>
-      </x:c>
-      <x:c r="C45" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D45" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>碰撞半径</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E45" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="str">
+        <x:v>War.DEFS.king.bodyRadius</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
       <x:c r="A46" s="1" t="str">
-        <x:v>War.DEFS.king.tier</x:v>
+        <x:v>僵尸之王</x:v>
       </x:c>
       <x:c r="B46" s="1" t="str">
-        <x:v>战争巨兽 / king / 时代</x:v>
-      </x:c>
-      <x:c r="C46" s="5" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D46" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>图标</x:v>
+      </x:c>
+      <x:c r="C46" s="5" t="str">
+        <x:v>assets/sprites/war_beasts.png#4,0,6,12</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E46" s="1" t="str">
-        <x:v>War.DEFS.king</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
+        <x:v>assets 图片路径；图集追加 #行,帧,总行数,总帧数（从0开始）</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="str">
+        <x:v>War.DEFS.king.icon</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="24" customHeight="1">
       <x:c r="A47" s="1" t="str">
-        <x:v>War.DEFS.cyst.hp</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B47" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 生命值</x:v>
-      </x:c>
-      <x:c r="C47" s="5" t="n">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="D47" s="6" t="n">
-        <x:v>60000</x:v>
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C47" s="5" t="str">
+        <x:v>尸变体血月囊肿</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E47" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="str">
+        <x:v>War.DEFS.cyst.name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="36" customHeight="1">
       <x:c r="A48" s="1" t="str">
-        <x:v>War.DEFS.cyst.dmg</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B48" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 伤害</x:v>
-      </x:c>
-      <x:c r="C48" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D48" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>描述</x:v>
+      </x:c>
+      <x:c r="C48" s="5" t="str">
+        <x:v>地图中央阻挡地面敌军 · 三条生命×60000（合计180000） · 每次破裂重创敌军，不伤基地</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E48" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
+        <x:v>文本，可直接修改</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="str">
+        <x:v>War.DEFS.cyst.desc</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="1" t="str">
-        <x:v>War.DEFS.cyst.range</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B49" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 攻击距离</x:v>
-      </x:c>
-      <x:c r="C49" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D49" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>生命值</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="n">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E49" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="str">
+        <x:v>War.DEFS.cyst.hp</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="1" t="str">
-        <x:v>War.DEFS.cyst.speed</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B50" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 移动速度</x:v>
-      </x:c>
-      <x:c r="C50" s="5" t="n">
+        <x:v>攻击伤害</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D50" s="6" t="n">
-        <x:v>0</x:v>
+      <x:c r="D50" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E50" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="str">
+        <x:v>War.DEFS.cyst.dmg</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="1" t="str">
-        <x:v>War.DEFS.cyst.atkCd</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B51" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 攻击间隔（秒）</x:v>
-      </x:c>
-      <x:c r="C51" s="5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D51" s="6" t="n">
-        <x:v>1</x:v>
+        <x:v>攻击距离</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E51" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="str">
+        <x:v>War.DEFS.cyst.range</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="1" t="str">
-        <x:v>War.DEFS.cyst.bodyRadius</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B52" s="1" t="str">
-        <x:v>战争巨兽 / cyst / bodyRadius</x:v>
-      </x:c>
-      <x:c r="C52" s="5" t="n">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D52" s="6" t="n">
-        <x:v>155</x:v>
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E52" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="str">
+        <x:v>War.DEFS.cyst.speed</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="1" t="str">
-        <x:v>War.DEFS.cyst.cost</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B53" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 旧金币基数（四资源价格另设）</x:v>
-      </x:c>
-      <x:c r="C53" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D53" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>攻击间隔（秒）</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E53" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="str">
+        <x:v>War.DEFS.cyst.atkCd</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="1" t="str">
-        <x:v>War.DEFS.cyst.pop</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B54" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 人口占用</x:v>
-      </x:c>
-      <x:c r="C54" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D54" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>碰撞半径</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="str">
+        <x:v>数值</x:v>
       </x:c>
       <x:c r="E54" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="str">
+        <x:v>War.DEFS.cyst.bodyRadius</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="24" customHeight="1">
       <x:c r="A55" s="1" t="str">
-        <x:v>War.DEFS.cyst.tier</x:v>
+        <x:v>尸变体血月囊肿</x:v>
       </x:c>
       <x:c r="B55" s="1" t="str">
-        <x:v>战争巨兽 / cyst / 时代</x:v>
-      </x:c>
-      <x:c r="C55" s="5" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D55" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>图标</x:v>
+      </x:c>
+      <x:c r="C55" s="5" t="str">
+        <x:v>assets/sprites/war_beasts.png#5,0,6,12</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="str">
+        <x:v>文本</x:v>
       </x:c>
       <x:c r="E55" s="1" t="str">
-        <x:v>War.DEFS.cyst</x:v>
+        <x:v>assets 图片路径；图集追加 #行,帧,总行数,总帧数（从0开始）</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="str">
+        <x:v>War.DEFS.cyst.icon</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="1" t="str">
+        <x:v>全阵营</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="str">
+        <x:v>触发时全队生命比例上限</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="str">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="str">
+        <x:v>war.triggerRatio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="1" t="str">
+        <x:v>全阵营</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="str">
+        <x:v>登场清兵半径</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="str">
+        <x:v>填写最终生效值</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="str">
+        <x:v>war.arrivalRadius</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R830524f46559481d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd23816f3bdf84d17"/>
   </x:tableParts>
 </x:worksheet>
 </file>